--- a/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVMUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="92">
   <si>
     <t>LVMUY</t>
   </si>
@@ -656,167 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -859,83 +865,89 @@
       <c r="P8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" s="3">
         <v>21349200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>39964800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>19533300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>38539800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>16704900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>30327600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>14249300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>26189700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>12408100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>20065100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>11963900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>33373900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>16312000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>29506500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>14998000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>29662400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>12603400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>23881500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>12178100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>25718300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>11647400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>22118900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>11601900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>23959800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>10726300</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,80 +993,86 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>12423900</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>12191800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>9635200</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>8845900</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>7638600</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3">
         <v>11295900</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="3">
         <v>9937100</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="3">
         <v>10048700</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>7828700</v>
       </c>
-      <c r="AI9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL9" s="3">
         <v>8866000</v>
       </c>
-      <c r="AK9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN9" s="3">
         <v>7720400</v>
       </c>
-      <c r="AM9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP9" s="3">
         <v>8359900</v>
       </c>
-      <c r="AO9" s="3" t="s">
+      <c r="AQ9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1100,80 +1118,86 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>27540900</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>26348000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>20692400</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>17343800</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>12426600</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3">
         <v>22078100</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3">
         <v>19569400</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="3">
         <v>19613700</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>16052800</v>
       </c>
-      <c r="AI10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="3">
         <v>16852300</v>
       </c>
-      <c r="AK10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="3">
         <v>14398500</v>
       </c>
-      <c r="AM10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP10" s="3">
         <v>15599900</v>
       </c>
-      <c r="AO10" s="3" t="s">
+      <c r="AQ10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1215,8 +1239,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1334,8 +1360,14 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1453,8 +1485,14 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1500,80 +1538,86 @@
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>117500</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>94300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>32800</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>150600</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="3">
         <v>136400</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>101600</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="3">
         <v>48200</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH14" s="3">
         <v>62700</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>80200</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL14" s="3">
         <v>150300</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN14" s="3">
         <v>111100</v>
       </c>
-      <c r="AM14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP14" s="3">
         <v>159600</v>
       </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AQ14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1616,11 +1660,11 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1682,17 +1726,23 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
-      <c r="AM15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN15" s="3" t="s">
-        <v>5</v>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="3">
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1731,8 +1781,10 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1778,80 +1830,86 @@
       <c r="Q17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>28945600</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>28179000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>22300500</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>19751500</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>18410200</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3">
         <v>26332100</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="3">
         <v>23341000</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH17" s="3">
         <v>23394200</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>18854900</v>
       </c>
-      <c r="AI17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL17" s="3">
         <v>20593000</v>
       </c>
-      <c r="AK17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN17" s="3">
         <v>18141500</v>
       </c>
-      <c r="AM17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP17" s="3">
         <v>19282200</v>
       </c>
-      <c r="AO17" s="3" t="s">
+      <c r="AQ17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1897,80 +1955,86 @@
       <c r="Q18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>11019200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>10360700</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>8027000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>6438200</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>1654900</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>7041800</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="3">
         <v>6165500</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="3">
         <v>6268200</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>5026600</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL18" s="3">
         <v>5125300</v>
       </c>
-      <c r="AK18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN18" s="3">
         <v>3977500</v>
       </c>
-      <c r="AM18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP18" s="3">
         <v>4677600</v>
       </c>
-      <c r="AO18" s="3" t="s">
+      <c r="AQ18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2012,8 +2076,10 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2059,80 +2125,86 @@
       <c r="Q20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>-725800</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>181000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>153400</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>4000</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-268400</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-151800</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="3">
         <v>20000</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-332400</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>56000</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL20" s="3">
         <v>57200</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN20" s="3">
         <v>66200</v>
       </c>
-      <c r="AM20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP20" s="3">
         <v>-248800</v>
       </c>
-      <c r="AO20" s="3" t="s">
+      <c r="AQ20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2184,74 +2256,80 @@
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>16862100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>12476500</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>10093400</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>8966500</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>7397900</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>6253100</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL21" s="3">
         <v>6715100</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN21" s="3">
         <v>5176900</v>
       </c>
-      <c r="AM21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP21" s="3">
         <v>5954700</v>
       </c>
-      <c r="AO21" s="3" t="s">
+      <c r="AQ21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2297,80 +2375,86 @@
       <c r="Q22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>142500</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>110600</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>140700</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>149600</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
         <v>235600</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>261500</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="3">
         <v>261200</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH22" s="3">
         <v>100500</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>80200</v>
       </c>
-      <c r="AI22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL22" s="3">
         <v>102100</v>
       </c>
-      <c r="AK22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN22" s="3">
         <v>87500</v>
       </c>
-      <c r="AM22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP22" s="3">
         <v>63400</v>
       </c>
-      <c r="AO22" s="3" t="s">
+      <c r="AQ22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2416,80 +2500,86 @@
       <c r="Q23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>10150900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>10431200</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>8039700</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>6292600</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>1150900</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3">
         <v>6628600</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF23" s="3">
         <v>5924400</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH23" s="3">
         <v>5835200</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>5002500</v>
       </c>
-      <c r="AI23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL23" s="3">
         <v>5080400</v>
       </c>
-      <c r="AK23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN23" s="3">
         <v>3956100</v>
       </c>
-      <c r="AM23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP23" s="3">
         <v>4365400</v>
       </c>
-      <c r="AO23" s="3" t="s">
+      <c r="AQ23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2535,80 +2625,86 @@
       <c r="Q24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>2595100</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>2710300</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>2128700</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>1893100</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB24" s="3">
         <v>557500</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="3">
         <v>1752300</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF24" s="3">
         <v>1683400</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH24" s="3">
         <v>1460900</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>1387900</v>
       </c>
-      <c r="AI24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL24" s="3">
         <v>1154500</v>
       </c>
-      <c r="AK24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN24" s="3">
         <v>1329600</v>
       </c>
-      <c r="AM24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP24" s="3">
         <v>1430900</v>
       </c>
-      <c r="AO24" s="3" t="s">
+      <c r="AQ24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2726,8 +2822,14 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2773,80 +2875,86 @@
       <c r="Q26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>7555800</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>7721000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>5911000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>4399500</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>593500</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="3">
         <v>4876300</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF26" s="3">
         <v>4240900</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH26" s="3">
         <v>4374400</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>3614600</v>
       </c>
-      <c r="AI26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL26" s="3">
         <v>3925800</v>
       </c>
-      <c r="AK26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN26" s="3">
         <v>2626600</v>
       </c>
-      <c r="AM26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP26" s="3">
         <v>2934500</v>
       </c>
-      <c r="AO26" s="3" t="s">
+      <c r="AQ26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2892,80 +3000,86 @@
       <c r="Q27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>7107500</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>7314400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>5607400</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>4169100</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>569500</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="3">
         <v>4556400</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF27" s="3">
         <v>3844500</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH27" s="3">
         <v>3962700</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>3298400</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL27" s="3">
         <v>3633000</v>
       </c>
-      <c r="AK27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN27" s="3">
         <v>2386500</v>
       </c>
-      <c r="AM27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP27" s="3">
         <v>2664500</v>
       </c>
-      <c r="AO27" s="3" t="s">
+      <c r="AQ27" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3083,8 +3197,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3127,11 +3247,11 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -3202,8 +3322,14 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3321,8 +3447,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3440,8 +3572,14 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3487,80 +3625,86 @@
       <c r="Q32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>725800</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>-181000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>-153400</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>268400</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>151800</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH32" s="3">
         <v>332400</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-57200</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN32" s="3">
         <v>-66200</v>
       </c>
-      <c r="AM32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP32" s="3">
         <v>248800</v>
       </c>
-      <c r="AO32" s="3" t="s">
+      <c r="AQ32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3606,80 +3750,86 @@
       <c r="Q33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>7107500</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>7314400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>5607400</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>4169100</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>569500</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="3">
         <v>4556400</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF33" s="3">
         <v>3844500</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH33" s="3">
         <v>3962700</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>3298400</v>
       </c>
-      <c r="AI33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL33" s="3">
         <v>3633000</v>
       </c>
-      <c r="AK33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN33" s="3">
         <v>2386500</v>
       </c>
-      <c r="AM33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP33" s="3">
         <v>2664500</v>
       </c>
-      <c r="AO33" s="3" t="s">
+      <c r="AQ33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3797,8 +3947,14 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3844,204 +4000,216 @@
       <c r="Q35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>7107500</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>7314400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>5607400</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>4169100</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>569500</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="3">
         <v>4556400</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF35" s="3">
         <v>3844500</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH35" s="3">
         <v>3962700</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>3298400</v>
       </c>
-      <c r="AI35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL35" s="3">
         <v>3633000</v>
       </c>
-      <c r="AK35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN35" s="3">
         <v>2386500</v>
       </c>
-      <c r="AM35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP35" s="3">
         <v>2664500</v>
       </c>
-      <c r="AO35" s="3" t="s">
+      <c r="AQ35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4083,8 +4251,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4126,56 +4296,58 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7772200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7843900</v>
+      </c>
+      <c r="F41" s="3">
         <v>10325200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>10318000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9601900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8837000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9971000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>10741700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7666300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7719300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>8592900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8228200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6708500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>6676400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>7801600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
@@ -4203,98 +4375,104 @@
       <c r="AA41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3">
         <v>6622700</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF41" s="3">
         <v>4704400</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH41" s="3">
         <v>5453200</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>4635800</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL41" s="3">
         <v>4194000</v>
       </c>
-      <c r="AK41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN41" s="3">
         <v>9479700</v>
       </c>
-      <c r="AM41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP41" s="3">
         <v>4160000</v>
       </c>
-      <c r="AO41" s="3" t="s">
+      <c r="AQ41" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6181900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>6238900</v>
+      </c>
+      <c r="F42" s="3">
         <v>5548900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>5545000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>4897200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>4507100</v>
       </c>
-      <c r="H42" s="3">
-        <v>4118400</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
+        <v>4119500</v>
+      </c>
+      <c r="K42" s="3">
         <v>4436800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>4223700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>4252900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>3884200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>3719300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>4625500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>4603400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>3830300</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
@@ -4322,98 +4500,104 @@
       <c r="AA42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3">
         <v>855700</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>927000</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3">
         <v>787800</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>799300</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL42" s="3">
         <v>577800</v>
       </c>
-      <c r="AK42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN42" s="3">
         <v>572200</v>
       </c>
-      <c r="AM42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP42" s="3">
         <v>439000</v>
       </c>
-      <c r="AO42" s="3" t="s">
+      <c r="AQ42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7555100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>7624800</v>
+      </c>
+      <c r="F43" s="3">
         <v>8789500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>8783300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>8758700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8061000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>9085800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>9788100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>8540700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>8599600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>8780800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>8408100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>7742400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>7705300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>7598600</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
@@ -4441,98 +4625,104 @@
       <c r="AA43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
         <v>6420800</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="3">
         <v>5759700</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH43" s="3">
         <v>5939300</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>4967400</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL43" s="3">
         <v>5413600</v>
       </c>
-      <c r="AK43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN43" s="3">
         <v>4061600</v>
       </c>
-      <c r="AM43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP43" s="3">
         <v>4816100</v>
       </c>
-      <c r="AO43" s="3" t="s">
+      <c r="AQ43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>27629400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>27884200</v>
+      </c>
+      <c r="F44" s="3">
         <v>26604400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>26585700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>27116900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>24956800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>24504600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>26398600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>26031300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>26211000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>25369700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>24293000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>24714000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>24595800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>21715300</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
@@ -4560,98 +4750,104 @@
       <c r="AA44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
         <v>16013400</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" s="3">
         <v>15953200</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH44" s="3">
         <v>14768500</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>13047500</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL44" s="3">
         <v>12216200</v>
       </c>
-      <c r="AK44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN44" s="3">
         <v>12190400</v>
       </c>
-      <c r="AM44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP44" s="3">
         <v>12379000</v>
       </c>
-      <c r="AO44" s="3" t="s">
+      <c r="AQ44" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2989800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3017400</v>
+      </c>
+      <c r="F45" s="3">
         <v>4446400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>4443300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1361100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1252700</v>
       </c>
-      <c r="H45" s="3">
-        <v>598400</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
+        <v>597400</v>
+      </c>
+      <c r="K45" s="3">
         <v>644700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>807900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>813500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>934000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>894400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1288200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1282100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>869900</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
@@ -4679,98 +4875,104 @@
       <c r="AA45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="3">
         <v>1035500</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="3">
         <v>1014100</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH45" s="3">
         <v>909700</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>888300</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL45" s="3">
         <v>1228600</v>
       </c>
-      <c r="AK45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN45" s="3">
         <v>1173600</v>
       </c>
-      <c r="AM45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP45" s="3">
         <v>975400</v>
       </c>
-      <c r="AO45" s="3" t="s">
+      <c r="AQ45" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>53097200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>53587000</v>
+      </c>
+      <c r="F46" s="3">
         <v>56568000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>56528200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>52729300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>48529000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>49146900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>52945600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>48134600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>48466900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>48314400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>46263800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>45853700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>45634500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>42470900</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
@@ -4798,98 +5000,104 @@
       <c r="AA46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD46" s="3">
         <v>30948000</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF46" s="3">
         <v>28358300</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH46" s="3">
         <v>27858500</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>24338300</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL46" s="3">
         <v>23630200</v>
       </c>
-      <c r="AK46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN46" s="3">
         <v>27477500</v>
       </c>
-      <c r="AM46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP46" s="3">
         <v>22769600</v>
       </c>
-      <c r="AO46" s="3" t="s">
+      <c r="AQ46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3651300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3685000</v>
+      </c>
+      <c r="F47" s="3">
         <v>3649200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>3646600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>3409300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>3137700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>3084200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>3322600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2715100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2733800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2604200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2493600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2699800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>2686900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>2324500</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4917,98 +5125,104 @@
       <c r="AA47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>3162500</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="3">
         <v>2750400</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH47" s="3">
         <v>2862600</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>2390300</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL47" s="3">
         <v>2257400</v>
       </c>
-      <c r="AK47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN47" s="3">
         <v>2228300</v>
       </c>
-      <c r="AM47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP47" s="3">
         <v>2461500</v>
       </c>
-      <c r="AO47" s="3" t="s">
+      <c r="AQ47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>51862200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>52340600</v>
+      </c>
+      <c r="F48" s="3">
         <v>52351800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>52314900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>52997100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>48775400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>48147800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>51869300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>47777800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>48107700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>47540600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>45522900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>43245600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>43038900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>40258600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
@@ -5036,98 +5250,104 @@
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>35699400</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>32928600</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3">
         <v>17876000</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>15549900</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL48" s="3">
         <v>30370000</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN48" s="3">
         <v>27241900</v>
       </c>
-      <c r="AM48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP48" s="3">
         <v>14248900</v>
       </c>
-      <c r="AO48" s="3" t="s">
+      <c r="AQ48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>47860200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>48301600</v>
+      </c>
+      <c r="F49" s="3">
         <v>48660300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>48626100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>50978300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>46917400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>48231700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>51959600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>50652500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>51002300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>54837000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>52509500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>55044800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>54781600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>53664600</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
@@ -5155,50 +5375,56 @@
       <c r="AA49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>39234300</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF49" s="3">
         <v>39610600</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH49" s="3">
         <v>36647400</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>34095100</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL49" s="3">
         <v>68466100</v>
       </c>
-      <c r="AK49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN49" s="3">
         <v>56139900</v>
       </c>
-      <c r="AM49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP49" s="3">
         <v>27861600</v>
       </c>
-      <c r="AO49" s="3" t="s">
+      <c r="AQ49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5316,8 +5542,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5435,56 +5667,62 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>855700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>863600</v>
+      </c>
+      <c r="F52" s="3">
         <v>890000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>889400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1052300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>968400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>860300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>926800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>851800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>857700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>853300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>817100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>845000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>840900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>793000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5512,50 +5750,56 @@
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>3619000</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>3315100</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>2645000</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>2396900</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL52" s="3">
         <v>2273200</v>
       </c>
-      <c r="AK52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN52" s="3">
         <v>2462800</v>
       </c>
-      <c r="AM52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP52" s="3">
         <v>2643400</v>
       </c>
-      <c r="AO52" s="3" t="s">
+      <c r="AQ52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5673,56 +5917,62 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>161966200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>163460200</v>
+      </c>
+      <c r="F54" s="3">
         <v>166768800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>166651400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>166265400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>153021000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>154457000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>166395300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>154772300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>155841000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>158830600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>152089300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>152156100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>151428700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>143898700</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
@@ -5750,50 +6000,56 @@
       <c r="AA54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3">
         <v>112663200</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF54" s="3">
         <v>106963000</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH54" s="3">
         <v>87889500</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>78770500</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL54" s="3">
         <v>78264400</v>
       </c>
-      <c r="AK54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN54" s="3">
         <v>73859500</v>
       </c>
-      <c r="AM54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP54" s="3">
         <v>69984900</v>
       </c>
-      <c r="AO54" s="3" t="s">
+      <c r="AQ54" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5835,8 +6091,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5878,56 +6136,58 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9032300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9115600</v>
+      </c>
+      <c r="F57" s="3">
         <v>9654800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9648000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9085100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>8361400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>8934700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>9625300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>8796700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>8857500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>10002200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>9577700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>8978200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>8935200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>9391900</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5955,98 +6215,104 @@
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>6787300</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>6073800</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>6285900</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>5059600</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL57" s="3">
         <v>5092700</v>
       </c>
-      <c r="AK57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN57" s="3">
         <v>4320800</v>
       </c>
-      <c r="AM57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP57" s="3">
         <v>4911200</v>
       </c>
-      <c r="AO57" s="3" t="s">
+      <c r="AQ57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12102100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>12213800</v>
+      </c>
+      <c r="F58" s="3">
         <v>12842600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>12833500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>15345900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>14123400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>14770700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>15912300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>16050600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>16161400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>15320000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>14669800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>17861400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>17776000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>13178400</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
@@ -6074,98 +6340,104 @@
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>11395100</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="3">
         <v>11668700</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH58" s="3">
         <v>5924000</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>6213600</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL58" s="3">
         <v>5487700</v>
       </c>
-      <c r="AK58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN58" s="3">
         <v>5463000</v>
       </c>
-      <c r="AM58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP58" s="3">
         <v>4013300</v>
       </c>
-      <c r="AO58" s="3" t="s">
+      <c r="AQ58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7791600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7863500</v>
+      </c>
+      <c r="F59" s="3">
         <v>8238800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>8233000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>7074600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>6511000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>6308100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>6795700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>6018400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>6060000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>6453000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>6179100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>6852600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>6819900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>6874000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6193,98 +6465,104 @@
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>8227900</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>7018400</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH59" s="3">
         <v>7701900</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>6037900</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL59" s="3">
         <v>6679200</v>
       </c>
-      <c r="AK59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN59" s="3">
         <v>5213900</v>
       </c>
-      <c r="AM59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP59" s="3">
         <v>6112000</v>
       </c>
-      <c r="AO59" s="3" t="s">
+      <c r="AQ59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32564800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>32865200</v>
+      </c>
+      <c r="F60" s="3">
         <v>35712100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>35687000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>35745200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>32897800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>34885600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>37582000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>34849500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>35090100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>36636500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>35081500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>37434500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>37255500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>33710600</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
@@ -6312,98 +6590,104 @@
       <c r="AA60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD60" s="3">
         <v>26410300</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF60" s="3">
         <v>24760900</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH60" s="3">
         <v>19911800</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>17311100</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL60" s="3">
         <v>16817500</v>
       </c>
-      <c r="AK60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN60" s="3">
         <v>14997600</v>
       </c>
-      <c r="AM60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP60" s="3">
         <v>15036500</v>
       </c>
-      <c r="AO60" s="3" t="s">
+      <c r="AQ60" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30341600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>30621500</v>
+      </c>
+      <c r="F61" s="3">
         <v>30340500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>30319100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>31283600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>28791600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>27991500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>30155000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>27719900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>27911300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>27784900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>26605600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>24015300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>23900500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>24917200</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -6432,97 +6716,103 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>18064500</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>18501200</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>7103300</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>7347800</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>7905500</v>
       </c>
-      <c r="AK61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
         <v>9213800</v>
       </c>
-      <c r="AM61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP61" s="3">
         <v>4615400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10652300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>10750600</v>
+      </c>
+      <c r="F62" s="3">
         <v>10814800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>10807200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>11517300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>10599900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>11570600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>12464900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>12634700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>12722000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>16679600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>15971600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>17234700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>17152300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>16682700</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
@@ -6550,50 +6840,56 @@
       <c r="AA62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>23400700</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>22068100</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>20706700</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>19544400</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL62" s="3">
         <v>19458700</v>
       </c>
-      <c r="AK62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN62" s="3">
         <v>17915900</v>
       </c>
-      <c r="AM62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP62" s="3">
         <v>17580200</v>
       </c>
-      <c r="AO62" s="3" t="s">
+      <c r="AQ62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6711,8 +7007,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6830,8 +7132,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6949,56 +7257,62 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>82343200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>83102700</v>
+      </c>
+      <c r="F66" s="3">
         <v>85814300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>85753800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>87727500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>80739300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>82723900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>89117800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>83541200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>84118000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>89524700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>85725000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>87255500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>86838300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>83404900</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
@@ -7026,50 +7340,56 @@
       <c r="AA66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>69952400</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>67344200</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH66" s="3">
         <v>49690100</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>45841500</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL66" s="3">
         <v>45761500</v>
       </c>
-      <c r="AK66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN66" s="3">
         <v>43746400</v>
       </c>
-      <c r="AM66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP66" s="3">
         <v>39004500</v>
       </c>
-      <c r="AO66" s="3" t="s">
+      <c r="AQ66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7111,8 +7431,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7230,8 +7552,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7349,8 +7677,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7468,8 +7802,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7587,56 +7927,62 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6508600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>6568700</v>
+      </c>
+      <c r="F72" s="3">
         <v>12772100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>12763100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>6691700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>6158700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>12993100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>13997300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>7786300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>7840100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>16771300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>16059500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>9257600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>9213400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>15052900</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
@@ -7664,50 +8010,56 @@
       <c r="AA72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>38341200</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>35396700</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3">
         <v>34086400</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>29060800</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL72" s="3">
         <v>28350400</v>
       </c>
-      <c r="AK72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN72" s="3">
         <v>25598200</v>
       </c>
-      <c r="AM72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP72" s="3">
         <v>25760400</v>
       </c>
-      <c r="AO72" s="3" t="s">
+      <c r="AQ72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7825,8 +8177,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7944,8 +8302,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8063,56 +8427,62 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>77796200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>78513800</v>
+      </c>
+      <c r="F76" s="3">
         <v>79220400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>79164600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>76682300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>70573900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>69900600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>75303400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>69436400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>69915800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>67444500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>64581900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>63009800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>62708600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>58898200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
@@ -8140,50 +8510,56 @@
       <c r="AA76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3">
         <v>42710900</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="3">
         <v>39618800</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH76" s="3">
         <v>38199400</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>32929000</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL76" s="3">
         <v>32502900</v>
       </c>
-      <c r="AK76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN76" s="3">
         <v>30113100</v>
       </c>
-      <c r="AM76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP76" s="3">
         <v>30980400</v>
       </c>
-      <c r="AO76" s="3" t="s">
+      <c r="AQ76" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8301,132 +8677,144 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8472,80 +8860,86 @@
       <c r="Q81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>7107500</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>7314400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>5607400</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>4169100</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>569500</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="3">
         <v>4556400</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF81" s="3">
         <v>3844500</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH81" s="3">
         <v>3962700</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>3298400</v>
       </c>
-      <c r="AI81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL81" s="3">
         <v>3633000</v>
       </c>
-      <c r="AK81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN81" s="3">
         <v>2386500</v>
       </c>
-      <c r="AM81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP81" s="3">
         <v>2664500</v>
       </c>
-      <c r="AO81" s="3" t="s">
+      <c r="AQ81" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8587,127 +8981,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1916000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1763400</v>
+      </c>
+      <c r="F83" s="3">
         <v>1344300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1448200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1681100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1692700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1318100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1262200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1566600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1559100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1216200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1124700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1447300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1538000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>780200</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>6320300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>6034300</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>3203400</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>2781000</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1462100</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>1170500</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL83" s="3">
         <v>1532600</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN83" s="3">
         <v>1133200</v>
       </c>
-      <c r="AM83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP83" s="3">
         <v>1526000</v>
       </c>
-      <c r="AO83" s="3" t="s">
+      <c r="AQ83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8825,8 +9227,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8944,8 +9352,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9063,8 +9477,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9182,8 +9602,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9301,127 +9727,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4368200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4408500</v>
+      </c>
+      <c r="F89" s="3">
         <v>6453600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>6449000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>4627700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>4259100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>6025500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>6491200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3902300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>3929200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>6438600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>6165300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>3684500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>3666900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>5646600</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>20216300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>10868700</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>8707700</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>4927900</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>6303700</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>3470800</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL89" s="3">
         <v>5345200</v>
       </c>
-      <c r="AK89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN89" s="3">
         <v>2542400</v>
       </c>
-      <c r="AM89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP89" s="3">
         <v>5407700</v>
       </c>
-      <c r="AO89" s="3" t="s">
+      <c r="AQ89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9463,127 +9901,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-872400</v>
+        <v>-1177300</v>
       </c>
       <c r="E91" s="3">
-        <v>-871800</v>
+        <v>-1188200</v>
       </c>
       <c r="F91" s="3">
+        <v>-1295600</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-1294700</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1385800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1275400</v>
       </c>
-      <c r="H91" s="3">
-        <v>-1028600</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
+        <v>-1451000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1108100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1461500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1471600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1792300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1716200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1945400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1936100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1343900</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1197000</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-1978800</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-2034800</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-1961200</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-1038700</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-1257800</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-861700</v>
       </c>
-      <c r="AM91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP91" s="3">
         <v>-1928600</v>
       </c>
-      <c r="AO91" s="3" t="s">
+      <c r="AQ91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9701,8 +10147,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9820,127 +10272,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1029400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1038900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1284500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1283600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1439800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1325100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1747100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1882100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1695100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1706800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-2329500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2230600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2235300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-2224600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2071200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-17322800</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-2931400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-2896300</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-3985600</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-2602400</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-8053600</v>
       </c>
-      <c r="AK94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-1603300</v>
       </c>
-      <c r="AM94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP94" s="3">
         <v>-1367500</v>
       </c>
-      <c r="AO94" s="3" t="s">
+      <c r="AQ94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9982,127 +10446,135 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2116400</v>
+      </c>
+      <c r="E96" s="3">
+        <v>2135900</v>
+      </c>
+      <c r="F96" s="3">
         <v>1603300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>1602100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>2192600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>2017900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>1421000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>1530800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>2007400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>2021300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>1518700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>1454300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>1912100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>1903000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>1338600</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-4510900</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-2427700</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1367000</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-2837500</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1190000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-1876500</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-902100</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-1465300</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-826400</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10220,8 +10692,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10339,8 +10817,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10458,361 +10942,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4376800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-4417200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-4772200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-4768900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-3973600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-3657000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2987400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-3218300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2649200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2667500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2976100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-2849800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-2190000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-2179500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-3660900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-16430600</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>7383800</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-3917800</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-1621100</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-3320400</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-1664600</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN100" s="3">
         <v>4794300</v>
       </c>
-      <c r="AM100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP100" s="3">
         <v>-3366500</v>
       </c>
-      <c r="AO100" s="3" t="s">
+      <c r="AQ100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-68700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-63200</v>
+      </c>
+      <c r="F101" s="3">
         <v>32100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>34600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>9600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>9700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-21600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-20600</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-127700</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-127100</v>
       </c>
       <c r="L101" s="3">
         <v>-127700</v>
       </c>
       <c r="M101" s="3">
+        <v>-127100</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-127700</v>
+      </c>
+      <c r="O101" s="3">
         <v>-117200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>153700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>163300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>212100</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>539900</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-1049300</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>28000</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3">
         <v>17600</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH101" s="3">
         <v>45000</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>31800</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-30300</v>
       </c>
-      <c r="AK101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN101" s="3">
         <v>-97600</v>
       </c>
-      <c r="AM101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AO101" s="3" t="s">
+      <c r="AQ101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1017400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1026700</v>
+      </c>
+      <c r="F102" s="3">
         <v>319900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>319700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-854400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-786300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1323100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1425400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-432300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-435300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1111400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1064200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-868400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-864300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-213200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>-12997300</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>14271800</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>1921600</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-661100</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>425800</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>477600</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL102" s="3">
         <v>-5270000</v>
       </c>
-      <c r="AK102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN102" s="3">
         <v>5585300</v>
       </c>
-      <c r="AM102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP102" s="3">
         <v>672600</v>
       </c>
-      <c r="AO102" s="3" t="s">
+      <c r="AQ102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
